--- a/Ozrit HR data/ozrit/HR/HR/Employees/Flutter/Visweshwar reddy/Salary details.xlsx
+++ b/Ozrit HR data/ozrit/HR/HR/Employees/Flutter/Visweshwar reddy/Salary details.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixld\Downloads\ozrit\Ozrit HR data\ozrit\HR\HR\Employees\Flutter\Visweshwar reddy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\HR\Employees\Flutter\Visweshwar reddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE80D014-EBEE-424E-92A5-EF1125CFC928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965AFF46-FD3E-4D8A-A475-4900F049874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">Month </t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t xml:space="preserve">Left </t>
+  </si>
+  <si>
+    <t>2500(liquid cash)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 - gas </t>
   </si>
 </sst>
 </file>
@@ -187,6 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -196,7 +203,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,32 +493,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
@@ -532,13 +538,13 @@
       <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F7" s="1" t="s">
@@ -615,7 +621,12 @@
       <c r="F10" s="1">
         <v>7079</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>

--- a/Ozrit HR data/ozrit/HR/HR/Employees/Flutter/Visweshwar reddy/Salary details.xlsx
+++ b/Ozrit HR data/ozrit/HR/HR/Employees/Flutter/Visweshwar reddy/Salary details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\HR\Employees\Flutter\Visweshwar reddy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965AFF46-FD3E-4D8A-A475-4900F049874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BE7FC8-8469-4A31-A075-8DD02143A2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Month </t>
   </si>
@@ -91,6 +91,21 @@
   </si>
   <si>
     <t xml:space="preserve">300 - gas </t>
+  </si>
+  <si>
+    <t>10.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October </t>
+  </si>
+  <si>
+    <t>7079(internet Payment)</t>
+  </si>
+  <si>
+    <t>3350(chairs amount)</t>
+  </si>
+  <si>
+    <t>7571(left)</t>
   </si>
 </sst>
 </file>
@@ -629,13 +644,30 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>28200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46200</v>
+      </c>
+      <c r="E11" s="1">
+        <v>18000</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
